--- a/source-data/Enerium_Герои.xlsx
+++ b/source-data/Enerium_Герои.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -199,7 +199,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fd36dda94fa62f6a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">07803d62df93af80 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -463,12 +463,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">физ ДД ловкости</t>
+          <t xml:space="preserve">физ ДД силы</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Огонь</t>
+          <t xml:space="preserve">без стихии</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -636,12 +636,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">контроль (на дебаффы)</t>
+          <t xml:space="preserve">контроль (на контроль)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1195,11 +1190,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент огненного крыла Иллюзориума, отчисленный в тот же день, когда спустился туда, куда студентам хода нет. Отчисленному одна дорога — в шахту.</t>
+          <t xml:space="preserve">Студент огненного крыла Иллюзориума, отчисленный с первого курса: огонь у него выходил раньше, чем он его звал. Отчисленному одна дорога — в шахту.</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">

--- a/source-data/Enerium_Герои.xlsx
+++ b/source-data/Enerium_Герои.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -199,7 +199,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">07803d62df93af80 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">af60ea8272e70424 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -302,8 +302,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
